--- a/04_DESIGN_TABLES/DesignTable_6404.xlsx
+++ b/04_DESIGN_TABLES/DesignTable_6404.xlsx
@@ -1027,10 +1027,14 @@
       </c>
       <c r="K11" s="3" t="inlineStr">
         <is>
-          <t>Air-Way s94 only (double-pass 26 rows); female ORB port profile per SAE J1926 (standard, in StandardsData); L32@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!L1747 Overall Length = 1.580 (table had 1.1) [user 2026-09-25: OMi dims &gt; Air-Way, ASSUMED]</t>
-        </is>
-      </c>
-      <c r="L11" s="3" t="inlineStr"/>
+          <t>Air-Way s94 only (double-pass 26 rows); female ORB port profile per SAE J1926 (standard, in StandardsData); L32@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!L1747 Overall Length = 1.580 (table had 1.1) [user 2026-09-25: OMi dims &gt; Air-Way, ASSUMED]; D1@BORE: OMi WebsitePartsInfo2026.xlsx Items!S1747 = 0.531 (table had 0.5) [user 2026-10-18 A19]</t>
+        </is>
+      </c>
+      <c r="L11" s="3" t="inlineStr">
+        <is>
+          <t>A19 (user 2026-10-18, group 3 open): D1@BORE 0.5 -&gt; OMi 0.531 (Items!S1747, M069) | A11 (user 2026-10-18): OMi bore 0.531 wider than the -06 port drill 0.50 -&gt; capped at 0.50 (report to OMi)</t>
+        </is>
+      </c>
       <c r="M11" t="inlineStr">
         <is>
           <t>BUILD</t>
@@ -1078,7 +1082,7 @@
       </c>
       <c r="J12" s="3" t="inlineStr">
         <is>
-          <t>ASSUMED</t>
+          <t>VERIFIED</t>
         </is>
       </c>
       <c r="K12" s="3" t="inlineStr">
@@ -1086,7 +1090,11 @@
           <t>Air-Way s94 only (double-pass 26 rows); female ORB port profile per SAE J1926 (standard, in StandardsData)</t>
         </is>
       </c>
-      <c r="L12" s="3" t="inlineStr"/>
+      <c r="L12" s="3" t="inlineStr">
+        <is>
+          <t>A23 (user 2026-10-18): VERIFIED - OMi = Air-Way on L32@DRIVE=1.5~1.500; C1HEX@HEX=1~1.000</t>
+        </is>
+      </c>
       <c r="M12" t="inlineStr">
         <is>
           <t>BUILD</t>

--- a/04_DESIGN_TABLES/DesignTable_6404.xlsx
+++ b/04_DESIGN_TABLES/DesignTable_6404.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -549,7 +549,7 @@
         </is>
       </c>
       <c r="B3" s="3" t="n">
-        <v>1.06</v>
+        <v>1.13</v>
       </c>
       <c r="C3" s="3" t="n">
         <v>0.6899999999999999</v>
@@ -583,10 +583,14 @@
       </c>
       <c r="K3" s="3" t="inlineStr">
         <is>
-          <t>Air-Way s94 only (double-pass 26 rows); female ORB port profile per SAE J1926 (standard, in StandardsData); L32@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!L1743 Overall Length = 1.060 (table had 1.13) [user 2026-09-25: OMi dims &gt; Air-Way, ASSUMED]</t>
-        </is>
-      </c>
-      <c r="L3" s="3" t="inlineStr"/>
+          <t>Air-Way s94 only (double-pass 26 rows); female ORB port profile per SAE J1926 (standard, in StandardsData); L32@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!L1743 Overall Length = 1.060 (table had 1.13) [user 2026-09-25: OMi dims &gt; Air-Way, ASSUMED]; L32@DRIVE: Air-Way 1.13 (raw 07_RAW_EXTRACTS; OMi file / Brennan 1.06) [OMi 2026-10-20 (Triveni): Air-Way over Brennan where Air-Way gives a value, incl. the numbers of OMi's website parts file (= Brennan data)]</t>
+        </is>
+      </c>
+      <c r="L3" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-20 Air-Way first: L32@DRIVE OMi/Brennan 1.06 -&gt; Air-Way 1.13</t>
+        </is>
+      </c>
       <c r="M3" t="inlineStr">
         <is>
           <t>BUILD</t>
@@ -605,7 +609,7 @@
         </is>
       </c>
       <c r="B4" s="3" t="n">
-        <v>1.34</v>
+        <v>1.31</v>
       </c>
       <c r="C4" s="3" t="n">
         <v>0.6899999999999999</v>
@@ -639,10 +643,14 @@
       </c>
       <c r="K4" s="3" t="inlineStr">
         <is>
-          <t>Air-Way s94 only (double-pass 26 rows); female ORB port profile per SAE J1926 (standard, in StandardsData); L32@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!L1744 Overall Length = 1.340 (table had 1.31) [user 2026-09-25: OMi dims &gt; Air-Way, ASSUMED]</t>
-        </is>
-      </c>
-      <c r="L4" s="3" t="inlineStr"/>
+          <t>Air-Way s94 only (double-pass 26 rows); female ORB port profile per SAE J1926 (standard, in StandardsData); L32@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!L1744 Overall Length = 1.340 (table had 1.31) [user 2026-09-25: OMi dims &gt; Air-Way, ASSUMED]; L32@DRIVE: Air-Way 1.31 (raw 07_RAW_EXTRACTS; OMi file / Brennan 1.34) [OMi 2026-10-20 (Triveni): Air-Way over Brennan where Air-Way gives a value, incl. the numbers of OMi's website parts file (= Brennan data)]</t>
+        </is>
+      </c>
+      <c r="L4" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-20 Air-Way first: L32@DRIVE OMi/Brennan 1.34 -&gt; Air-Way 1.31</t>
+        </is>
+      </c>
       <c r="M4" t="inlineStr">
         <is>
           <t>BUILD</t>
@@ -881,7 +889,7 @@
         </is>
       </c>
       <c r="B9" s="3" t="n">
-        <v>1.59</v>
+        <v>1.38</v>
       </c>
       <c r="C9" s="3" t="n">
         <v>0.88</v>
@@ -915,10 +923,14 @@
       </c>
       <c r="K9" s="3" t="inlineStr">
         <is>
-          <t>Air-Way s94 only (double-pass 26 rows); female ORB port profile per SAE J1926 (standard, in StandardsData); L32@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!L1745 Overall Length = 1.590 (table had 1.38) [user 2026-09-25: OMi dims &gt; Air-Way, ASSUMED]</t>
-        </is>
-      </c>
-      <c r="L9" s="3" t="inlineStr"/>
+          <t>Air-Way s94 only (double-pass 26 rows); female ORB port profile per SAE J1926 (standard, in StandardsData); L32@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!L1745 Overall Length = 1.590 (table had 1.38) [user 2026-09-25: OMi dims &gt; Air-Way, ASSUMED]; L32@DRIVE: Air-Way 1.38 (raw 07_RAW_EXTRACTS; OMi file / Brennan 1.59) [OMi 2026-10-20 (Triveni): Air-Way over Brennan where Air-Way gives a value, incl. the numbers of OMi's website parts file (= Brennan data)]</t>
+        </is>
+      </c>
+      <c r="L9" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-20 Air-Way first: L32@DRIVE OMi/Brennan 1.59 -&gt; Air-Way 1.38</t>
+        </is>
+      </c>
       <c r="M9" t="inlineStr">
         <is>
           <t>BUILD</t>
@@ -940,7 +952,7 @@
         <v>1.38</v>
       </c>
       <c r="C10" s="3" t="n">
-        <v>0.8129999999999999</v>
+        <v>0.88</v>
       </c>
       <c r="D10" s="3" t="n">
         <v>0.5</v>
@@ -971,10 +983,14 @@
       </c>
       <c r="K10" s="3" t="inlineStr">
         <is>
-          <t>Air-Way s94 only (double-pass 26 rows); female ORB port profile per SAE J1926 (standard, in StandardsData); C1HEX@HEX: OMi WebsitePartsInfo2026.xlsx Items!R1746 Hex Flat = 0.813 (table had 0.88) [user 2026-09-25: OMi dims &gt; Air-Way, ASSUMED]</t>
-        </is>
-      </c>
-      <c r="L10" s="3" t="inlineStr"/>
+          <t>Air-Way s94 only (double-pass 26 rows); female ORB port profile per SAE J1926 (standard, in StandardsData); C1HEX@HEX: OMi WebsitePartsInfo2026.xlsx Items!R1746 Hex Flat = 0.813 (table had 0.88) [user 2026-09-25: OMi dims &gt; Air-Way, ASSUMED]; C1HEX@HEX: Air-Way 0.88 (raw 07_RAW_EXTRACTS; OMi file / Brennan 0.813) [OMi 2026-10-20 (Triveni): Air-Way over Brennan where Air-Way gives a value, incl. the numbers of OMi's website parts file (= Brennan data)]</t>
+        </is>
+      </c>
+      <c r="L10" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-20 Air-Way first: C1HEX@HEX OMi/Brennan 0.813 -&gt; Air-Way 0.88</t>
+        </is>
+      </c>
       <c r="M10" t="inlineStr">
         <is>
           <t>BUILD</t>
@@ -993,7 +1009,7 @@
         </is>
       </c>
       <c r="B11" s="3" t="n">
-        <v>1.58</v>
+        <v>1.1</v>
       </c>
       <c r="C11" s="3" t="n">
         <v>0.88</v>
@@ -1027,12 +1043,12 @@
       </c>
       <c r="K11" s="3" t="inlineStr">
         <is>
-          <t>Air-Way s94 only (double-pass 26 rows); female ORB port profile per SAE J1926 (standard, in StandardsData); L32@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!L1747 Overall Length = 1.580 (table had 1.1) [user 2026-09-25: OMi dims &gt; Air-Way, ASSUMED]; D1@BORE: OMi WebsitePartsInfo2026.xlsx Items!S1747 = 0.531 (table had 0.5) [user 2026-10-18 A19]</t>
+          <t>Air-Way s94 only (double-pass 26 rows); female ORB port profile per SAE J1926 (standard, in StandardsData); L32@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!L1747 Overall Length = 1.580 (table had 1.1) [user 2026-09-25: OMi dims &gt; Air-Way, ASSUMED]; D1@BORE: OMi WebsitePartsInfo2026.xlsx Items!S1747 = 0.531 (table had 0.5) [user 2026-10-18 A19]; L32@DRIVE: Air-Way 1.1 (raw 07_RAW_EXTRACTS; OMi file / Brennan 1.58) [OMi 2026-10-20 (Triveni): Air-Way over Brennan where Air-Way gives a value, incl. the numbers of OMi's website parts file (= Brennan data)]</t>
         </is>
       </c>
       <c r="L11" s="3" t="inlineStr">
         <is>
-          <t>A19 (user 2026-10-18, group 3 open): D1@BORE 0.5 -&gt; OMi 0.531 (Items!S1747, M069) | A11 (user 2026-10-18): OMi bore 0.531 wider than the -06 port drill 0.50 -&gt; capped at 0.50 (report to OMi)</t>
+          <t>A19 (user 2026-10-18, group 3 open): D1@BORE 0.5 -&gt; OMi 0.531 (Items!S1747, M069) | A11 (user 2026-10-18): OMi bore 0.531 wider than the -06 port drill 0.50 -&gt; capped at 0.50 (report to OMi) | 2026-10-20 Air-Way first: L32@DRIVE OMi/Brennan 1.58 -&gt; Air-Way 1.1</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
@@ -1113,10 +1129,10 @@
         </is>
       </c>
       <c r="B13" s="3" t="n">
-        <v>1.65</v>
+        <v>1.69</v>
       </c>
       <c r="C13" s="3" t="n">
-        <v>1.063</v>
+        <v>1</v>
       </c>
       <c r="D13" s="3" t="n">
         <v>0.68</v>
@@ -1147,10 +1163,14 @@
       </c>
       <c r="K13" s="3" t="inlineStr">
         <is>
-          <t>Air-Way s94 only (double-pass 26 rows); female ORB port profile per SAE J1926 (standard, in StandardsData); L32@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!L1749 Overall Length = 1.650 (table had 1.69); C1HEX@HEX: OMi WebsitePartsInfo2026.xlsx Items!R1749 Hex Flat = 1.063 (table had 1) [user 2026-09-25: OMi dims &gt; Air-Way, ASSUMED]</t>
-        </is>
-      </c>
-      <c r="L13" s="3" t="inlineStr"/>
+          <t>Air-Way s94 only (double-pass 26 rows); female ORB port profile per SAE J1926 (standard, in StandardsData); L32@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!L1749 Overall Length = 1.650 (table had 1.69); C1HEX@HEX: OMi WebsitePartsInfo2026.xlsx Items!R1749 Hex Flat = 1.063 (table had 1) [user 2026-09-25: OMi dims &gt; Air-Way, ASSUMED]; L32@DRIVE: Air-Way 1.69 (raw 07_RAW_EXTRACTS; OMi file / Brennan 1.65) [OMi 2026-10-20 (Triveni): Air-Way over Brennan where Air-Way gives a value, incl. the numbers of OMi's website parts file (= Brennan data)]; C1HEX@HEX: Air-Way 1 (raw 07_RAW_EXTRACTS; OMi file / Brennan 1.063) [OMi 2026-10-20 (Triveni): Air-Way over Brennan where Air-Way gives a value, incl. the numbers of OMi's website parts file (= Brennan data)]</t>
+        </is>
+      </c>
+      <c r="L13" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-20 Air-Way first: L32@DRIVE OMi/Brennan 1.65 -&gt; Air-Way 1.69 | 2026-10-20 Air-Way first: C1HEX@HEX OMi/Brennan 1.063 -&gt; Air-Way 1</t>
+        </is>
+      </c>
       <c r="M13" t="inlineStr">
         <is>
           <t>BUILD</t>
@@ -1279,7 +1299,7 @@
         </is>
       </c>
       <c r="B16" s="3" t="n">
-        <v>1.75</v>
+        <v>1.81</v>
       </c>
       <c r="C16" s="3" t="n">
         <v>1.25</v>
@@ -1313,10 +1333,14 @@
       </c>
       <c r="K16" s="3" t="inlineStr">
         <is>
-          <t>Air-Way s94 only (double-pass 26 rows); female ORB port profile per SAE J1926 (standard, in StandardsData); L32@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!L1751 Overall Length = 1.750 (table had 1.81) [user 2026-09-25: OMi dims &gt; Air-Way, ASSUMED]</t>
-        </is>
-      </c>
-      <c r="L16" s="3" t="inlineStr"/>
+          <t>Air-Way s94 only (double-pass 26 rows); female ORB port profile per SAE J1926 (standard, in StandardsData); L32@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!L1751 Overall Length = 1.750 (table had 1.81) [user 2026-09-25: OMi dims &gt; Air-Way, ASSUMED]; L32@DRIVE: Air-Way 1.81 (raw 07_RAW_EXTRACTS; OMi file / Brennan 1.75) [OMi 2026-10-20 (Triveni): Air-Way over Brennan where Air-Way gives a value, incl. the numbers of OMi's website parts file (= Brennan data)]</t>
+        </is>
+      </c>
+      <c r="L16" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-20 Air-Way first: L32@DRIVE OMi/Brennan 1.75 -&gt; Air-Way 1.81</t>
+        </is>
+      </c>
       <c r="M16" t="inlineStr">
         <is>
           <t>BUILD</t>
@@ -1335,7 +1359,7 @@
         </is>
       </c>
       <c r="B17" s="3" t="n">
-        <v>1.85</v>
+        <v>1.72</v>
       </c>
       <c r="C17" s="3" t="n">
         <v>1.25</v>
@@ -1369,10 +1393,14 @@
       </c>
       <c r="K17" s="3" t="inlineStr">
         <is>
-          <t>Air-Way s94 only (double-pass 26 rows); female ORB port profile per SAE J1926 (standard, in StandardsData); L32@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!L1752 Overall Length = 1.850 (table had 1.72) [user 2026-09-25: OMi dims &gt; Air-Way, ASSUMED]</t>
-        </is>
-      </c>
-      <c r="L17" s="3" t="inlineStr"/>
+          <t>Air-Way s94 only (double-pass 26 rows); female ORB port profile per SAE J1926 (standard, in StandardsData); L32@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!L1752 Overall Length = 1.850 (table had 1.72) [user 2026-09-25: OMi dims &gt; Air-Way, ASSUMED]; L32@DRIVE: Air-Way 1.72 (raw 07_RAW_EXTRACTS; OMi file / Brennan 1.85) [OMi 2026-10-20 (Triveni): Air-Way over Brennan where Air-Way gives a value, incl. the numbers of OMi's website parts file (= Brennan data)]</t>
+        </is>
+      </c>
+      <c r="L17" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-20 Air-Way first: L32@DRIVE OMi/Brennan 1.85 -&gt; Air-Way 1.72</t>
+        </is>
+      </c>
       <c r="M17" t="inlineStr">
         <is>
           <t>BUILD</t>
@@ -1446,7 +1474,7 @@
         </is>
       </c>
       <c r="B19" s="3" t="n">
-        <v>1.96</v>
+        <v>1.97</v>
       </c>
       <c r="C19" s="3" t="n">
         <v>1.38</v>
@@ -1480,10 +1508,14 @@
       </c>
       <c r="K19" s="3" t="inlineStr">
         <is>
-          <t>Air-Way s94 only (double-pass 26 rows); female ORB port profile per SAE J1926 (standard, in StandardsData); L32@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!L1753 Overall Length = 1.960 (table had 1.97) [user 2026-09-25: OMi dims &gt; Air-Way, ASSUMED]</t>
-        </is>
-      </c>
-      <c r="L19" s="3" t="inlineStr"/>
+          <t>Air-Way s94 only (double-pass 26 rows); female ORB port profile per SAE J1926 (standard, in StandardsData); L32@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!L1753 Overall Length = 1.960 (table had 1.97) [user 2026-09-25: OMi dims &gt; Air-Way, ASSUMED]; L32@DRIVE: Air-Way 1.97 (raw 07_RAW_EXTRACTS; OMi file / Brennan 1.96) [OMi 2026-10-20 (Triveni): Air-Way over Brennan where Air-Way gives a value, incl. the numbers of OMi's website parts file (= Brennan data)]</t>
+        </is>
+      </c>
+      <c r="L19" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-20 Air-Way first: L32@DRIVE OMi/Brennan 1.96 -&gt; Air-Way 1.97</t>
+        </is>
+      </c>
       <c r="M19" t="inlineStr">
         <is>
           <t>BUILD</t>
@@ -1502,7 +1534,7 @@
         </is>
       </c>
       <c r="B20" s="3" t="n">
-        <v>1.98</v>
+        <v>1.97</v>
       </c>
       <c r="C20" s="3" t="n">
         <v>1.38</v>
@@ -1536,10 +1568,14 @@
       </c>
       <c r="K20" s="3" t="inlineStr">
         <is>
-          <t>Air-Way s94 only (double-pass 26 rows); female ORB port profile per SAE J1926 (standard, in StandardsData); L32@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!L1754 Overall Length = 1.980 (table had 1.97) [user 2026-09-25: OMi dims &gt; Air-Way, ASSUMED]</t>
-        </is>
-      </c>
-      <c r="L20" s="3" t="inlineStr"/>
+          <t>Air-Way s94 only (double-pass 26 rows); female ORB port profile per SAE J1926 (standard, in StandardsData); L32@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!L1754 Overall Length = 1.980 (table had 1.97) [user 2026-09-25: OMi dims &gt; Air-Way, ASSUMED]; L32@DRIVE: Air-Way 1.97 (raw 07_RAW_EXTRACTS; OMi file / Brennan 1.98) [OMi 2026-10-20 (Triveni): Air-Way over Brennan where Air-Way gives a value, incl. the numbers of OMi's website parts file (= Brennan data)]</t>
+        </is>
+      </c>
+      <c r="L20" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-20 Air-Way first: L32@DRIVE OMi/Brennan 1.98 -&gt; Air-Way 1.97</t>
+        </is>
+      </c>
       <c r="M20" t="inlineStr">
         <is>
           <t>BUILD</t>
@@ -1613,7 +1649,7 @@
         </is>
       </c>
       <c r="B22" s="3" t="n">
-        <v>1.91</v>
+        <v>1.97</v>
       </c>
       <c r="C22" s="3" t="n">
         <v>1.63</v>
@@ -1647,10 +1683,14 @@
       </c>
       <c r="K22" s="3" t="inlineStr">
         <is>
-          <t>Air-Way s94 only (double-pass 26 rows); female ORB port profile per SAE J1926 (standard, in StandardsData); L32@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!L1755 Overall Length = 1.910 (table had 1.97) [user 2026-09-25: OMi dims &gt; Air-Way, ASSUMED]</t>
-        </is>
-      </c>
-      <c r="L22" s="3" t="inlineStr"/>
+          <t>Air-Way s94 only (double-pass 26 rows); female ORB port profile per SAE J1926 (standard, in StandardsData); L32@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!L1755 Overall Length = 1.910 (table had 1.97) [user 2026-09-25: OMi dims &gt; Air-Way, ASSUMED]; L32@DRIVE: Air-Way 1.97 (raw 07_RAW_EXTRACTS; OMi file / Brennan 1.91) [OMi 2026-10-20 (Triveni): Air-Way over Brennan where Air-Way gives a value, incl. the numbers of OMi's website parts file (= Brennan data)]</t>
+        </is>
+      </c>
+      <c r="L22" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-20 Air-Way first: L32@DRIVE OMi/Brennan 1.91 -&gt; Air-Way 1.97</t>
+        </is>
+      </c>
       <c r="M22" t="inlineStr">
         <is>
           <t>BUILD</t>
@@ -1669,7 +1709,7 @@
         </is>
       </c>
       <c r="B23" s="3" t="n">
-        <v>2.1</v>
+        <v>2.16</v>
       </c>
       <c r="C23" s="3" t="n">
         <v>1.63</v>
@@ -1703,10 +1743,14 @@
       </c>
       <c r="K23" s="3" t="inlineStr">
         <is>
-          <t>Air-Way s94 only (double-pass 26 rows); female ORB port profile per SAE J1926 (standard, in StandardsData); L32@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!L1756 Overall Length = 2.100 (table had 2.16) [user 2026-09-25: OMi dims &gt; Air-Way, ASSUMED]</t>
-        </is>
-      </c>
-      <c r="L23" s="3" t="inlineStr"/>
+          <t>Air-Way s94 only (double-pass 26 rows); female ORB port profile per SAE J1926 (standard, in StandardsData); L32@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!L1756 Overall Length = 2.100 (table had 2.16) [user 2026-09-25: OMi dims &gt; Air-Way, ASSUMED]; L32@DRIVE: Air-Way 2.16 (raw 07_RAW_EXTRACTS; OMi file / Brennan 2.1) [OMi 2026-10-20 (Triveni): Air-Way over Brennan where Air-Way gives a value, incl. the numbers of OMi's website parts file (= Brennan data)]</t>
+        </is>
+      </c>
+      <c r="L23" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-20 Air-Way first: L32@DRIVE OMi/Brennan 2.1 -&gt; Air-Way 2.16</t>
+        </is>
+      </c>
       <c r="M23" t="inlineStr">
         <is>
           <t>BUILD</t>
@@ -1945,7 +1989,7 @@
         </is>
       </c>
       <c r="B28" s="3" t="n">
-        <v>2.23</v>
+        <v>2.3</v>
       </c>
       <c r="C28" s="3" t="n">
         <v>2.25</v>
@@ -1979,10 +2023,14 @@
       </c>
       <c r="K28" s="3" t="inlineStr">
         <is>
-          <t>Air-Way s94 only (double-pass 26 rows); female ORB port profile per SAE J1926 (standard, in StandardsData); L32@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!L1759 Overall Length = 2.230 (table had 2.3) [user 2026-09-25: OMi dims &gt; Air-Way, ASSUMED]</t>
-        </is>
-      </c>
-      <c r="L28" s="3" t="inlineStr"/>
+          <t>Air-Way s94 only (double-pass 26 rows); female ORB port profile per SAE J1926 (standard, in StandardsData); L32@DRIVE: OMi WebsitePartsInfo2026.xlsx Items!L1759 Overall Length = 2.230 (table had 2.3) [user 2026-09-25: OMi dims &gt; Air-Way, ASSUMED]; L32@DRIVE: Air-Way 2.3 (raw 07_RAW_EXTRACTS; OMi file / Brennan 2.23) [OMi 2026-10-20 (Triveni): Air-Way over Brennan where Air-Way gives a value, incl. the numbers of OMi's website parts file (= Brennan data)]</t>
+        </is>
+      </c>
+      <c r="L28" s="3" t="inlineStr">
+        <is>
+          <t>2026-10-20 Air-Way first: L32@DRIVE OMi/Brennan 2.23 -&gt; Air-Way 2.3</t>
+        </is>
+      </c>
       <c r="M28" t="inlineStr">
         <is>
           <t>BUILD</t>
